--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbInvestTrade001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbInvestTrade001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\guilin\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8700"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,9 +88,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>01 公允价值</t>
-  </si>
-  <si>
     <t>“币种”枚举值如下：</t>
   </si>
   <si>
@@ -94,7 +96,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CNY </t>
     </r>
@@ -114,7 +116,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">01 </t>
     </r>
@@ -134,7 +136,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">HKD </t>
     </r>
@@ -154,7 +156,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">02 </t>
     </r>
@@ -174,7 +176,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">USD </t>
     </r>
@@ -194,7 +196,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">03 </t>
     </r>
@@ -214,7 +216,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">EUR </t>
     </r>
@@ -234,7 +236,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">04 </t>
     </r>
@@ -254,7 +256,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">JPY </t>
     </r>
@@ -274,7 +276,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">05 </t>
     </r>
@@ -294,7 +296,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MOP </t>
     </r>
@@ -314,7 +316,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">06 </t>
     </r>
@@ -334,7 +336,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CHF </t>
     </r>
@@ -354,7 +356,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">07 </t>
     </r>
@@ -374,7 +376,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GBP </t>
     </r>
@@ -394,7 +396,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">08 </t>
     </r>
@@ -414,7 +416,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">RUB </t>
     </r>
@@ -434,7 +436,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">09 </t>
     </r>
@@ -454,7 +456,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CAD </t>
     </r>
@@ -474,7 +476,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">10 </t>
     </r>
@@ -494,7 +496,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">DKK </t>
     </r>
@@ -514,7 +516,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">11 </t>
     </r>
@@ -534,7 +536,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AUD </t>
     </r>
@@ -554,7 +556,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">12 </t>
     </r>
@@ -574,7 +576,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SEK </t>
     </r>
@@ -594,7 +596,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SGD </t>
     </r>
@@ -614,7 +616,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TWD </t>
     </r>
@@ -634,7 +636,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AED </t>
     </r>
@@ -654,7 +656,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AFN </t>
     </r>
@@ -674,7 +676,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ALL </t>
     </r>
@@ -694,7 +696,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AMD </t>
     </r>
@@ -714,7 +716,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ANG </t>
     </r>
@@ -734,7 +736,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AOA </t>
     </r>
@@ -754,7 +756,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ARS </t>
     </r>
@@ -774,7 +776,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AWG </t>
     </r>
@@ -794,7 +796,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">AZN </t>
     </r>
@@ -814,7 +816,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BAM </t>
     </r>
@@ -834,7 +836,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BBD </t>
     </r>
@@ -854,7 +856,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BDT </t>
     </r>
@@ -874,7 +876,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BGN </t>
     </r>
@@ -894,7 +896,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BHD </t>
     </r>
@@ -914,7 +916,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BIF </t>
     </r>
@@ -934,7 +936,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BMD </t>
     </r>
@@ -954,7 +956,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BND </t>
     </r>
@@ -974,7 +976,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BOB </t>
     </r>
@@ -994,7 +996,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BOV </t>
     </r>
@@ -1012,7 +1014,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>Mvdol</t>
     </r>
@@ -1032,7 +1034,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BRL </t>
     </r>
@@ -1052,7 +1054,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BSD </t>
     </r>
@@ -1072,7 +1074,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BTN </t>
     </r>
@@ -1092,7 +1094,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BWP </t>
     </r>
@@ -1112,7 +1114,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BYR </t>
     </r>
@@ -1132,7 +1134,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">BZD </t>
     </r>
@@ -1152,7 +1154,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CDF </t>
     </r>
@@ -1172,7 +1174,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>CHE WIR</t>
     </r>
@@ -1192,7 +1194,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>CHW WIR</t>
     </r>
@@ -1212,7 +1214,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CLF </t>
     </r>
@@ -1230,7 +1232,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>UF</t>
     </r>
@@ -1250,7 +1252,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CLP </t>
     </r>
@@ -1270,7 +1272,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">COP </t>
     </r>
@@ -1290,7 +1292,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">COU </t>
     </r>
@@ -1308,7 +1310,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>UVR</t>
     </r>
@@ -1328,7 +1330,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CRC </t>
     </r>
@@ -1348,7 +1350,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CUC </t>
     </r>
@@ -1368,7 +1370,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CUP </t>
     </r>
@@ -1388,7 +1390,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CVE </t>
     </r>
@@ -1408,7 +1410,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">CZK </t>
     </r>
@@ -1428,7 +1430,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">DJF </t>
     </r>
@@ -1448,7 +1450,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">DOP </t>
     </r>
@@ -1468,7 +1470,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">DZD </t>
     </r>
@@ -1488,7 +1490,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">EGP </t>
     </r>
@@ -1508,7 +1510,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ERN </t>
     </r>
@@ -1528,7 +1530,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ETB </t>
     </r>
@@ -1548,7 +1550,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">FJD </t>
     </r>
@@ -1568,7 +1570,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">FKP </t>
     </r>
@@ -1588,7 +1590,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GEL </t>
     </r>
@@ -1608,7 +1610,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GHS </t>
     </r>
@@ -1628,7 +1630,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GIP </t>
     </r>
@@ -1648,7 +1650,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GMD </t>
     </r>
@@ -1668,7 +1670,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GNF </t>
     </r>
@@ -1688,7 +1690,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GTQ </t>
     </r>
@@ -1708,7 +1710,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">GYD </t>
     </r>
@@ -1728,7 +1730,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">HNL </t>
     </r>
@@ -1748,7 +1750,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">HRK </t>
     </r>
@@ -1768,7 +1770,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">HTG </t>
     </r>
@@ -1788,7 +1790,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">HUF </t>
     </r>
@@ -1808,7 +1810,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">IDR </t>
     </r>
@@ -1828,7 +1830,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ILS </t>
     </r>
@@ -1848,7 +1850,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">INR </t>
     </r>
@@ -1868,7 +1870,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">IQD </t>
     </r>
@@ -1888,7 +1890,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">IRR </t>
     </r>
@@ -1908,7 +1910,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ISK </t>
     </r>
@@ -1928,7 +1930,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">JMD </t>
     </r>
@@ -1948,7 +1950,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">JOD </t>
     </r>
@@ -1968,7 +1970,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KES </t>
     </r>
@@ -1988,7 +1990,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KGS </t>
     </r>
@@ -2008,7 +2010,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KHR </t>
     </r>
@@ -2028,7 +2030,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KMF </t>
     </r>
@@ -2048,7 +2050,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KPW </t>
     </r>
@@ -2068,7 +2070,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KRW </t>
     </r>
@@ -2088,7 +2090,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KWD </t>
     </r>
@@ -2108,7 +2110,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KYD </t>
     </r>
@@ -2128,7 +2130,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">KZT </t>
     </r>
@@ -2148,7 +2150,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LAK </t>
     </r>
@@ -2168,7 +2170,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LBP </t>
     </r>
@@ -2188,7 +2190,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LKR </t>
     </r>
@@ -2208,7 +2210,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LRD </t>
     </r>
@@ -2228,7 +2230,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LSL </t>
     </r>
@@ -2248,7 +2250,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">LYD </t>
     </r>
@@ -2268,7 +2270,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MAD </t>
     </r>
@@ -2288,7 +2290,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MDL </t>
     </r>
@@ -2308,7 +2310,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MGA </t>
     </r>
@@ -2328,7 +2330,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MKD </t>
     </r>
@@ -2348,7 +2350,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MMK </t>
     </r>
@@ -2368,7 +2370,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MNT </t>
     </r>
@@ -2388,7 +2390,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MRO </t>
     </r>
@@ -2408,7 +2410,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MUR </t>
     </r>
@@ -2428,7 +2430,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MVR </t>
     </r>
@@ -2448,7 +2450,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MWK </t>
     </r>
@@ -2468,7 +2470,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MXN </t>
     </r>
@@ -2488,7 +2490,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MXV </t>
     </r>
@@ -2506,7 +2508,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>UDI</t>
     </r>
@@ -2526,7 +2528,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MYR </t>
     </r>
@@ -2546,7 +2548,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">MZN </t>
     </r>
@@ -2566,7 +2568,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NAD </t>
     </r>
@@ -2586,7 +2588,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NGN </t>
     </r>
@@ -2606,7 +2608,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NIO </t>
     </r>
@@ -2626,7 +2628,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NOK </t>
     </r>
@@ -2646,7 +2648,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NPR </t>
     </r>
@@ -2666,7 +2668,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">NZD </t>
     </r>
@@ -2686,7 +2688,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">OMR </t>
     </r>
@@ -2706,7 +2708,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PAB </t>
     </r>
@@ -2726,7 +2728,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PEN </t>
     </r>
@@ -2746,7 +2748,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PGK </t>
     </r>
@@ -2766,7 +2768,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PHP </t>
     </r>
@@ -2786,7 +2788,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PKR </t>
     </r>
@@ -2806,7 +2808,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PLN </t>
     </r>
@@ -2826,7 +2828,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">PYG </t>
     </r>
@@ -2846,7 +2848,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">QAR </t>
     </r>
@@ -2866,7 +2868,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">RON </t>
     </r>
@@ -2886,7 +2888,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">RSD </t>
     </r>
@@ -2906,7 +2908,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">RWF </t>
     </r>
@@ -2926,7 +2928,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SAR </t>
     </r>
@@ -2946,7 +2948,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SBD </t>
     </r>
@@ -2966,7 +2968,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SCR </t>
     </r>
@@ -2986,7 +2988,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SDG </t>
     </r>
@@ -3006,7 +3008,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SHP </t>
     </r>
@@ -3026,7 +3028,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SLL </t>
     </r>
@@ -3046,7 +3048,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SOS </t>
     </r>
@@ -3066,7 +3068,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SRD </t>
     </r>
@@ -3086,7 +3088,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SSP </t>
     </r>
@@ -3106,7 +3108,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">STD </t>
     </r>
@@ -3126,7 +3128,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SVC </t>
     </r>
@@ -3146,7 +3148,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SYP </t>
     </r>
@@ -3166,7 +3168,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">SZL </t>
     </r>
@@ -3186,7 +3188,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">THB </t>
     </r>
@@ -3206,7 +3208,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TJS </t>
     </r>
@@ -3226,7 +3228,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TMT </t>
     </r>
@@ -3246,7 +3248,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TND </t>
     </r>
@@ -3266,7 +3268,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TOP </t>
     </r>
@@ -3286,7 +3288,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TRY </t>
     </r>
@@ -3306,7 +3308,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TTD </t>
     </r>
@@ -3326,7 +3328,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">TZS </t>
     </r>
@@ -3346,7 +3348,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">UAH </t>
     </r>
@@ -3366,7 +3368,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">UGX </t>
     </r>
@@ -3386,7 +3388,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">USN </t>
     </r>
@@ -3406,7 +3408,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">UYI </t>
     </r>
@@ -3424,7 +3426,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>URUIURUI</t>
     </r>
@@ -3444,7 +3446,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">UYU </t>
     </r>
@@ -3464,7 +3466,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">UZS </t>
     </r>
@@ -3484,7 +3486,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">VEF </t>
     </r>
@@ -3504,7 +3506,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">VND </t>
     </r>
@@ -3524,7 +3526,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">VUV </t>
     </r>
@@ -3544,7 +3546,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">WST </t>
     </r>
@@ -3564,7 +3566,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XAF </t>
     </r>
@@ -3584,7 +3586,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XAG </t>
     </r>
@@ -3604,7 +3606,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XAU </t>
     </r>
@@ -3624,7 +3626,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XBA </t>
     </r>
@@ -3644,7 +3646,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XBB </t>
     </r>
@@ -3664,7 +3666,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XBC </t>
     </r>
@@ -3682,7 +3684,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>9</t>
     </r>
@@ -3702,7 +3704,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XBD </t>
     </r>
@@ -3720,7 +3722,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>17</t>
     </r>
@@ -3740,7 +3742,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XCD </t>
     </r>
@@ -3760,7 +3762,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XDR </t>
     </r>
@@ -3780,7 +3782,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XOF </t>
     </r>
@@ -3800,7 +3802,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XPD </t>
     </r>
@@ -3820,7 +3822,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XPF </t>
     </r>
@@ -3838,7 +3840,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>CFP</t>
     </r>
@@ -3858,7 +3860,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XPT </t>
     </r>
@@ -3878,7 +3880,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XSU </t>
     </r>
@@ -3898,7 +3900,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XTS </t>
     </r>
@@ -3918,7 +3920,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XUA </t>
     </r>
@@ -3938,7 +3940,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">XXX </t>
     </r>
@@ -3958,7 +3960,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">YER </t>
     </r>
@@ -3978,7 +3980,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ZAR </t>
     </r>
@@ -3998,7 +4000,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ZMW </t>
     </r>
@@ -4018,7 +4020,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">ZWL </t>
     </r>
@@ -4031,20 +4033,20 @@
       </rPr>
       <t>津巴布韦元</t>
     </r>
+  </si>
+  <si>
+    <t>交易发起时间</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4063,151 +4065,7 @@
       <sz val="10.5"/>
       <color rgb="FF080808"/>
       <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -4215,8 +4073,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4229,194 +4093,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4424,251 +4102,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4679,61 +4115,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4782,7 +4174,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4817,7 +4209,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5020,36 +4412,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.2685185185185" customWidth="1"/>
-    <col min="2" max="2" width="14.0925925925926" customWidth="1"/>
-    <col min="3" max="3" width="19.7222222222222" customWidth="1"/>
-    <col min="4" max="4" width="14.2685185185185" customWidth="1"/>
-    <col min="5" max="5" width="18.2685185185185" customWidth="1"/>
-    <col min="6" max="6" width="17.1759259259259" customWidth="1"/>
-    <col min="8" max="8" width="13.9074074074074" customWidth="1"/>
-    <col min="9" max="9" width="12.8148148148148" customWidth="1"/>
-    <col min="10" max="10" width="18.8148148148148" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="17.9074074074074" customWidth="1"/>
-    <col min="13" max="13" width="21.0925925925926" customWidth="1"/>
+    <col min="12" max="12" width="17.90625" customWidth="1"/>
+    <col min="13" max="13" width="21.08984375" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="13.2685185185185" customWidth="1"/>
-    <col min="16" max="16" width="15.2685185185185" customWidth="1"/>
-    <col min="17" max="17" width="9" style="3"/>
-    <col min="19" max="19" width="9" style="3"/>
-    <col min="21" max="21" width="9" style="3"/>
+    <col min="15" max="15" width="13.26953125" customWidth="1"/>
+    <col min="16" max="16" width="17.08984375" customWidth="1"/>
+    <col min="17" max="17" width="15.26953125" customWidth="1"/>
+    <col min="18" max="18" width="9" style="3"/>
+    <col min="20" max="20" width="9" style="3"/>
+    <col min="22" max="22" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5096,991 +4489,1000 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="8:8">
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>Sheet3!$B$3:$B$14</formula1>
-    </dataValidation>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"01 公允价值,02 摊余成本"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
-      <formula1>Sheet3!$A$3:$A$180</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet3!$B$3:$B$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet3!$A$3:$A$180</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:B180"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
+    <row r="49" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
+    <row r="53" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
+    <row r="54" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
+    <row r="59" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
+    <row r="61" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="2" t="s">
+    <row r="69" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="2" t="s">
+    <row r="70" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="2" t="s">
+    <row r="71" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="2" t="s">
+    <row r="73" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="2" t="s">
+    <row r="76" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="2" t="s">
+    <row r="79" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2" t="s">
+    <row r="82" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
+    <row r="83" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="2" t="s">
+    <row r="84" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="2" t="s">
+    <row r="85" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2" t="s">
+    <row r="86" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
+    <row r="87" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2" t="s">
+    <row r="88" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2" t="s">
+    <row r="89" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="2" t="s">
+    <row r="90" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="2" t="s">
+    <row r="91" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="2" t="s">
+    <row r="92" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2" t="s">
+    <row r="94" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2" t="s">
+    <row r="95" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
+    <row r="96" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="2" t="s">
+    <row r="97" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="2" t="s">
+    <row r="98" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="2" t="s">
+    <row r="99" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2" t="s">
+    <row r="100" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2" t="s">
+    <row r="101" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="2" t="s">
+    <row r="102" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="2" t="s">
+    <row r="103" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="2" t="s">
+    <row r="104" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="2" t="s">
+    <row r="105" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="2" t="s">
+    <row r="106" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="2" t="s">
+    <row r="107" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="2" t="s">
+    <row r="108" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="2" t="s">
+    <row r="110" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
+    <row r="111" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2" t="s">
+    <row r="112" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="2" t="s">
+    <row r="113" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="2" t="s">
+    <row r="114" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="2" t="s">
+    <row r="115" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="2" t="s">
+    <row r="116" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="2" t="s">
+    <row r="117" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="2" t="s">
+    <row r="118" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="2" t="s">
+    <row r="119" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="2" t="s">
+    <row r="120" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="2" t="s">
+    <row r="121" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="2" t="s">
+    <row r="122" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="2" t="s">
+    <row r="123" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
+    <row r="124" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
+    <row r="125" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="2" t="s">
+    <row r="126" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="2" t="s">
+    <row r="127" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="2" t="s">
+    <row r="128" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="2" t="s">
+    <row r="129" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="2" t="s">
+    <row r="130" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="2" t="s">
+    <row r="131" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="2" t="s">
+    <row r="132" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="2" t="s">
+    <row r="133" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="2" t="s">
+    <row r="134" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="2" t="s">
+    <row r="135" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="2" t="s">
+    <row r="136" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="2" t="s">
+    <row r="137" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="2" t="s">
+    <row r="138" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="2" t="s">
+    <row r="139" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="2" t="s">
+    <row r="140" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="2" t="s">
+    <row r="141" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="2" t="s">
+    <row r="142" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="2" t="s">
+    <row r="143" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="2" t="s">
+    <row r="144" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="2" t="s">
+    <row r="145" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="2" t="s">
+    <row r="146" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="2" t="s">
+    <row r="147" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="2" t="s">
+    <row r="148" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="2" t="s">
+    <row r="149" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="2" t="s">
+    <row r="150" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="2" t="s">
+    <row r="151" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="2" t="s">
+    <row r="152" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="2" t="s">
+    <row r="153" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="2" t="s">
+    <row r="154" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="2" t="s">
+    <row r="155" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="2" t="s">
+    <row r="156" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="2" t="s">
+    <row r="157" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="2" t="s">
+    <row r="158" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="2" t="s">
+    <row r="159" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="2" t="s">
+    <row r="160" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="2" t="s">
+    <row r="161" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="2" t="s">
+    <row r="162" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="2" t="s">
+    <row r="163" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="2" t="s">
+    <row r="164" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="2" t="s">
+    <row r="165" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="2" t="s">
+    <row r="166" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="2" t="s">
+    <row r="167" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="2" t="s">
+    <row r="168" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="2" t="s">
+    <row r="169" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="2" t="s">
+    <row r="170" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="2" t="s">
+    <row r="171" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="2" t="s">
+    <row r="172" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="2" t="s">
+    <row r="173" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="2" t="s">
+    <row r="174" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="2" t="s">
+    <row r="175" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="2" t="s">
+    <row r="176" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="2" t="s">
+    <row r="177" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="2" t="s">
+    <row r="178" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="2" t="s">
+    <row r="179" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="2" t="s">
+    <row r="180" spans="1:1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>